--- a/docs/データシート.xlsx
+++ b/docs/データシート.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yamashita\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yamashita\Documents\sensors-and-control\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08BB85CB-2E7E-4E1A-A439-3C916D47831B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0591E554-625C-4201-A201-928C6E1033F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{D7E328D4-FD25-4938-8122-60FB433CDBB7}"/>
+    <workbookView xWindow="11190" yWindow="0" windowWidth="11460" windowHeight="14410" xr2:uid="{D7E328D4-FD25-4938-8122-60FB433CDBB7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="23">
   <si>
     <t>公称値</t>
     <rPh sb="0" eb="3">
@@ -66,13 +66,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>表2</t>
-    <rPh sb="0" eb="1">
-      <t>ヒョウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>日中の窓際</t>
     <rPh sb="0" eb="2">
       <t>ニッチュウ</t>
@@ -97,13 +90,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>表3</t>
-    <rPh sb="0" eb="1">
-      <t>ヒョウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>距離</t>
     <rPh sb="0" eb="2">
       <t>キョリ</t>
@@ -205,6 +191,61 @@
     </rPh>
     <rPh sb="16" eb="21">
       <t>ジュンホウコウデンリュウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>表2 フォトレジスタの抵抗</t>
+    <rPh sb="0" eb="1">
+      <t>ヒョウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>テイコウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>表3 シャープペンシル線における距離と抵抗値の測定結果（HB）</t>
+    <rPh sb="0" eb="1">
+      <t>ヒョウ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>セン</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>キョリ</t>
+    </rPh>
+    <rPh sb="19" eb="22">
+      <t>テイコウチ</t>
+    </rPh>
+    <rPh sb="23" eb="27">
+      <t>ソクテイケッカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>実際の距離</t>
+    <rPh sb="0" eb="2">
+      <t>ジッサイ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>キョリ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>表5 超音波距離センサの測定結果</t>
+    <rPh sb="0" eb="1">
+      <t>ヒョウ</t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t>チョウオンパ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>キョリ</t>
+    </rPh>
+    <rPh sb="12" eb="16">
+      <t>ソクテイケッカ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -214,8 +255,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="179" formatCode="0.0"/>
-    <numFmt numFmtId="180" formatCode="0.0%"/>
+    <numFmt numFmtId="176" formatCode="0.0"/>
+    <numFmt numFmtId="177" formatCode="0.0%"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -287,35 +328,32 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -334,6 +372,2211 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ja-JP"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$G$9</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>抵抗値</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="38100" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-0.25409208223972002"/>
+                  <c:y val="4.6296296296296294E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="ja-JP"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$F$10:$F$19</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>100</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$G$10:$G$19</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>58.2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>107.2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>144.30000000000001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>189</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>253</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>305</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>373</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>446</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>511</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>561</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-A442-40C0-933E-E7C7F2067A2C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="256352768"/>
+        <c:axId val="256349408"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="256352768"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="110"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="ja-JP" altLang="en-US"/>
+                  <a:t>距離 </a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" altLang="ja-JP"/>
+                  <a:t>[mm]</a:t>
+                </a:r>
+                <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="ja-JP"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0.0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ja-JP"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="256349408"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="256349408"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="ja-JP" altLang="en-US"/>
+                  <a:t>抵抗値 </a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" altLang="ja-JP"/>
+                  <a:t>[kΩ]</a:t>
+                </a:r>
+                <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="ja-JP"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ja-JP"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="256352768"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ja-JP"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ja-JP"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$G$22</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>測定値</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="38100" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-0.14860411198600176"/>
+                  <c:y val="-1.5594925634295712E-3"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="ja-JP"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$F$23:$F$32</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>100</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$G$23:$G$32</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>37</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>47</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>56</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>67</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>77</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>86</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>96</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-76B7-40DF-AC32-E725A7D8EA17}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1183562880"/>
+        <c:axId val="1183563360"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1183562880"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="110"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="ja-JP" altLang="en-US"/>
+                  <a:t>実際の距離</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="ja-JP"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ja-JP"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1183563360"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1183563360"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="ja-JP" altLang="en-US"/>
+                  <a:t>測定値</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="ja-JP"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ja-JP"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1183562880"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ja-JP"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>22225</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>82550</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>631825</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>82550</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="グラフ 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{71513F23-7A5C-4690-8ACA-66E46BB21A85}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>98425</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>69850</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>69850</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="グラフ 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D0DEB0F9-23D2-1F24-BF16-32FAC3BF58C4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -653,28 +2896,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19DE7EFB-A6F4-4630-9E61-6FD08FA6A003}">
-  <dimension ref="B2:G21"/>
+  <dimension ref="B2:G32"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="2" width="8.6640625" style="3"/>
-    <col min="3" max="3" width="13" style="3" customWidth="1"/>
-    <col min="4" max="4" width="14.6640625" style="3" customWidth="1"/>
-    <col min="5" max="5" width="8.6640625" style="3"/>
-    <col min="6" max="6" width="13.6640625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="13.75" style="3" customWidth="1"/>
-    <col min="8" max="16384" width="8.6640625" style="3"/>
+    <col min="1" max="2" width="8.6640625" style="2"/>
+    <col min="3" max="3" width="13" style="2" customWidth="1"/>
+    <col min="4" max="4" width="14.6640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="8.6640625" style="2"/>
+    <col min="6" max="6" width="13.6640625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="13.75" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="8.6640625" style="2"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="F2" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="F2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G2" s="2"/>
+      <c r="G2" s="8"/>
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B3" s="1" t="s">
@@ -686,270 +2929,398 @@
       <c r="D3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="B4" s="3">
+      <c r="B4" s="2">
         <v>10</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="2">
         <v>10.4</v>
       </c>
-      <c r="D4" s="7">
+      <c r="D4" s="5">
         <f>(C4-B4)/B4</f>
         <v>4.0000000000000036E-2</v>
       </c>
-      <c r="F4" s="3" t="s">
-        <v>5</v>
+      <c r="F4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G4" s="2">
+        <v>114</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="B5" s="3">
+      <c r="B5" s="2">
         <v>100</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="2">
         <v>99.7</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="5">
         <f t="shared" ref="D5:D13" si="0">(C5-B5)/B5</f>
         <v>-2.9999999999999714E-3</v>
       </c>
-      <c r="F5" s="3" t="s">
-        <v>6</v>
+      <c r="F5" s="2" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="B6" s="3">
+      <c r="B6" s="2">
         <v>220</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="2">
         <v>220</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F6" s="3" t="s">
-        <v>7</v>
-      </c>
+      <c r="F6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G6" s="4"/>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="B7" s="3">
+      <c r="B7" s="2">
         <v>330</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="2">
         <v>325</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="5">
         <f t="shared" si="0"/>
         <v>-1.5151515151515152E-2</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="B8" s="3">
+      <c r="B8" s="2">
         <v>1000</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="2">
         <v>972</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="5">
         <f t="shared" si="0"/>
         <v>-2.8000000000000001E-2</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G8" s="2"/>
+      <c r="F8" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G8" s="8"/>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="B9" s="3">
+      <c r="B9" s="2">
         <v>2000</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="2">
         <v>1960</v>
       </c>
-      <c r="D9" s="7">
+      <c r="D9" s="5">
         <f t="shared" si="0"/>
         <v>-0.02</v>
       </c>
-      <c r="F9" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>10</v>
+      <c r="F9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="B10" s="3">
+      <c r="B10" s="2">
         <v>5100</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="2">
         <v>5120</v>
       </c>
-      <c r="D10" s="7">
+      <c r="D10" s="5">
         <f t="shared" si="0"/>
         <v>3.9215686274509803E-3</v>
       </c>
-      <c r="F10" s="4">
+      <c r="F10" s="3">
         <v>10</v>
+      </c>
+      <c r="G10" s="2">
+        <v>58.2</v>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="B11" s="3">
+      <c r="B11" s="2">
         <v>10000</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11" s="2">
         <v>10050</v>
       </c>
-      <c r="D11" s="7">
+      <c r="D11" s="5">
         <f t="shared" si="0"/>
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="F11" s="4">
+      <c r="F11" s="3">
         <v>20</v>
+      </c>
+      <c r="G11" s="2">
+        <v>107.2</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="B12" s="3">
+      <c r="B12" s="2">
         <v>100000</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="2">
         <v>100500</v>
       </c>
-      <c r="D12" s="7">
+      <c r="D12" s="5">
         <f t="shared" si="0"/>
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="F12" s="4">
+      <c r="F12" s="3">
         <v>30</v>
+      </c>
+      <c r="G12" s="2">
+        <v>144.30000000000001</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="B13" s="6">
+      <c r="B13" s="4">
         <v>1000000</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C13" s="4">
         <v>996000</v>
       </c>
-      <c r="D13" s="8">
+      <c r="D13" s="6">
         <f t="shared" si="0"/>
         <v>-4.0000000000000001E-3</v>
       </c>
-      <c r="F13" s="4">
+      <c r="F13" s="3">
         <v>40</v>
+      </c>
+      <c r="G13" s="2">
+        <v>189</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="F14" s="4">
+      <c r="F14" s="3">
         <v>50</v>
+      </c>
+      <c r="G14" s="2">
+        <v>253</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="B15" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="F15" s="4">
+      <c r="B15" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="F15" s="3">
         <v>60</v>
+      </c>
+      <c r="G15" s="2">
+        <v>305</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="F16" s="3">
+        <v>70</v>
+      </c>
+      <c r="G16" s="2">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="B17" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D16" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F16" s="4">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B17" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C17" s="3">
+      <c r="C17" s="2">
         <v>1.98</v>
       </c>
-      <c r="D17" s="4">
+      <c r="D17" s="3">
         <f>((5-C17)/220)*1000</f>
         <v>13.727272727272727</v>
       </c>
-      <c r="F17" s="4">
+      <c r="F17" s="3">
         <v>80</v>
       </c>
+      <c r="G17" s="2">
+        <v>446</v>
+      </c>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B18" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C18" s="3">
+    <row r="18" spans="2:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="B18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C18" s="2">
         <v>2.0499999999999998</v>
       </c>
-      <c r="D18" s="4">
+      <c r="D18" s="3">
         <f t="shared" ref="D18:D21" si="1">((5-C18)/220)*1000</f>
         <v>13.40909090909091</v>
       </c>
-      <c r="F18" s="4">
+      <c r="F18" s="3">
         <v>90</v>
       </c>
+      <c r="G18" s="2">
+        <v>511</v>
+      </c>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B19" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C19" s="3">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="B19" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C19" s="2">
         <v>2.74</v>
       </c>
-      <c r="D19" s="4">
+      <c r="D19" s="3">
         <f t="shared" si="1"/>
         <v>10.272727272727272</v>
       </c>
-      <c r="F19" s="4">
+      <c r="F19" s="7">
         <v>100</v>
       </c>
+      <c r="G19" s="4">
+        <v>561</v>
+      </c>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B20" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C20" s="3">
+    <row r="20" spans="2:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="B20" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C20" s="2">
         <v>2.74</v>
       </c>
-      <c r="D20" s="4">
+      <c r="D20" s="3">
         <f t="shared" si="1"/>
         <v>10.272727272727272</v>
       </c>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B21" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C21" s="6">
+    <row r="21" spans="2:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="B21" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21" s="4">
         <v>2.78</v>
       </c>
-      <c r="D21" s="9">
+      <c r="D21" s="7">
         <f t="shared" si="1"/>
         <v>10.090909090909092</v>
       </c>
+      <c r="F21" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G21" s="8"/>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="F22" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="F23" s="2">
+        <v>10</v>
+      </c>
+      <c r="G23" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="F24" s="2">
+        <v>20</v>
+      </c>
+      <c r="G24" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="F25" s="2">
+        <v>30</v>
+      </c>
+      <c r="G25" s="2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="F26" s="2">
+        <v>40</v>
+      </c>
+      <c r="G26" s="2">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="27" spans="2:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="F27" s="2">
+        <v>50</v>
+      </c>
+      <c r="G27" s="2">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="28" spans="2:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="F28" s="2">
+        <v>60</v>
+      </c>
+      <c r="G28" s="2">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="29" spans="2:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="F29" s="2">
+        <v>70</v>
+      </c>
+      <c r="G29" s="2">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="30" spans="2:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="F30" s="2">
+        <v>80</v>
+      </c>
+      <c r="G30" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="31" spans="2:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="F31" s="2">
+        <v>90</v>
+      </c>
+      <c r="G31" s="2">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="32" spans="2:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="F32" s="4">
+        <v>100</v>
+      </c>
+      <c r="G32" s="4">
+        <v>96</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="F2:G2"/>
     <mergeCell ref="F8:G8"/>
     <mergeCell ref="B15:D15"/>
+    <mergeCell ref="F21:G21"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/docs/データシート.xlsx
+++ b/docs/データシート.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yamashita\Documents\sensors-and-control\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0591E554-625C-4201-A201-928C6E1033F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A1A166F-34AD-4FFE-A563-E1046560A233}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11190" yWindow="0" windowWidth="11460" windowHeight="14410" xr2:uid="{D7E328D4-FD25-4938-8122-60FB433CDBB7}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" activeTab="1" xr2:uid="{D7E328D4-FD25-4938-8122-60FB433CDBB7}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="1st" sheetId="1" r:id="rId1"/>
+    <sheet name="3rd" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="49">
   <si>
     <t>公称値</t>
     <rPh sb="0" eb="3">
@@ -247,6 +248,182 @@
     <rPh sb="12" eb="16">
       <t>ソクテイケッカ</t>
     </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>表</t>
+    <rPh sb="0" eb="1">
+      <t>ヒョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>部品</t>
+    <rPh sb="0" eb="2">
+      <t>ブヒン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>型番・仕様</t>
+    <rPh sb="0" eb="2">
+      <t>カタバン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>シヨウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>個数</t>
+    <rPh sb="0" eb="2">
+      <t>コスウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>状態</t>
+    <rPh sb="0" eb="2">
+      <t>ジョウタイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>購入先</t>
+    <rPh sb="0" eb="3">
+      <t>コウニュウサキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>アナログマイクモジュール</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>サーボモータ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>超音波距離センサ</t>
+    <rPh sb="0" eb="5">
+      <t>チョウオンパキョリ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>赤外線センサ</t>
+    <rPh sb="0" eb="3">
+      <t>セキガイセン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>DCモーター</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>DRV8835モータードライバー</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>駆動輪（タイヤ付ホイール）</t>
+    <rPh sb="0" eb="3">
+      <t>クドウリン</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ツ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>自在キャスター</t>
+    <rPh sb="0" eb="2">
+      <t>ジザイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ごみ箱本体</t>
+    <rPh sb="2" eb="3">
+      <t>バコ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ホンタイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>電池ボックス（モーター用）</t>
+    <rPh sb="0" eb="2">
+      <t>デンチ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ヨウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Arduino用電源</t>
+    <rPh sb="7" eb="8">
+      <t>ヨウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>デンゲン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>モバイルバッテリー</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>単3×6本（9V）</t>
+    <rPh sb="0" eb="1">
+      <t>タン</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ホン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>軽量，小型</t>
+    <rPh sb="0" eb="2">
+      <t>ケイリョウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>コガタ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>HC-SR04</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>手持ち</t>
+    <rPh sb="0" eb="2">
+      <t>テモ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>追加購入</t>
+    <rPh sb="0" eb="4">
+      <t>ツイカコウニュウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>AE-DRV8835</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://www.amazon.co.jp/dp/B084VNV24C</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>-</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -258,7 +435,7 @@
     <numFmt numFmtId="176" formatCode="0.0"/>
     <numFmt numFmtId="177" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -277,6 +454,15 @@
     </font>
     <font>
       <sz val="6"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="游ゴシック"/>
       <family val="2"/>
       <charset val="128"/>
@@ -320,15 +506,18 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -356,9 +545,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="パーセント" xfId="1" builtinId="5"/>
+    <cellStyle name="ハイパーリンク" xfId="2" builtinId="8"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -399,7 +604,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$G$9</c:f>
+              <c:f>'1st'!$G$9</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -496,7 +701,7 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet1!$F$10:$F$19</c:f>
+              <c:f>'1st'!$F$10:$F$19</c:f>
               <c:numCache>
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="10"/>
@@ -535,7 +740,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!$G$10:$G$19</c:f>
+              <c:f>'1st'!$G$10:$G$19</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
@@ -668,7 +873,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="ja-JP"/>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -790,7 +995,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="ja-JP"/>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -912,7 +1117,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$G$22</c:f>
+              <c:f>'1st'!$G$22</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1009,7 +1214,7 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet1!$F$23:$F$32</c:f>
+              <c:f>'1st'!$F$23:$F$32</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
@@ -1048,7 +1253,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!$G$23:$G$32</c:f>
+              <c:f>'1st'!$G$23:$G$32</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
@@ -3323,4 +3528,215 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C64A3BAC-DF67-4C17-88FB-619D516E3C51}">
+  <dimension ref="B2:F14"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="1" max="1" width="8.6640625" style="10"/>
+    <col min="2" max="2" width="25.58203125" style="10" customWidth="1"/>
+    <col min="3" max="3" width="17.1640625" style="10" customWidth="1"/>
+    <col min="4" max="5" width="8.6640625" style="10"/>
+    <col min="6" max="6" width="38.58203125" style="10" customWidth="1"/>
+    <col min="7" max="16384" width="8.6640625" style="10"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:6" s="10" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B2" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+    </row>
+    <row r="3" spans="2:6" s="10" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B3" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6" s="10" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B4" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" s="10">
+        <v>3</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6" s="10" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B5" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" s="10">
+        <v>1</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6" s="10" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B6" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="D6" s="10">
+        <v>1</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6" s="10" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B7" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" s="10">
+        <v>1</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6" s="10" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B8" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8" s="10">
+        <v>2</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="9" spans="2:6" s="10" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B9" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="D9" s="10">
+        <v>1</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6" s="10" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B10" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" s="10">
+        <v>2</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6" s="10" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B11" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" s="10">
+        <v>2</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6" s="10" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B12" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="D12" s="10">
+        <v>1</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="13" spans="2:6" s="10" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B13" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="D13" s="10">
+        <v>1</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="14" spans="2:6" s="10" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B14" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="D14" s="13">
+        <v>1</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="F14" s="13" t="s">
+        <v>48</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:F2"/>
+  </mergeCells>
+  <phoneticPr fontId="2"/>
+  <hyperlinks>
+    <hyperlink ref="F4" r:id="rId1" xr:uid="{01866009-211E-45D4-BEBD-41C9FB273838}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/docs/データシート.xlsx
+++ b/docs/データシート.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yamashita\Documents\sensors-and-control\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A1A166F-34AD-4FFE-A563-E1046560A233}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7272ADF7-F6F9-4E46-9221-195CFD875705}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" activeTab="1" xr2:uid="{D7E328D4-FD25-4938-8122-60FB433CDBB7}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="11460" windowHeight="14410" xr2:uid="{D7E328D4-FD25-4938-8122-60FB433CDBB7}"/>
   </bookViews>
   <sheets>
     <sheet name="1st" sheetId="1" r:id="rId1"/>
@@ -543,9 +543,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -559,6 +556,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -3114,15 +3114,15 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="F2" s="8" t="s">
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="F2" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="G2" s="8"/>
+      <c r="G2" s="13"/>
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B3" s="1" t="s">
@@ -3173,6 +3173,9 @@
       <c r="F5" s="2" t="s">
         <v>5</v>
       </c>
+      <c r="G5" s="2">
+        <v>70551</v>
+      </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B6" s="2">
@@ -3188,7 +3191,9 @@
       <c r="F6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G6" s="4"/>
+      <c r="G6" s="4">
+        <v>320000</v>
+      </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B7" s="2">
@@ -3213,10 +3218,10 @@
         <f t="shared" si="0"/>
         <v>-2.8000000000000001E-2</v>
       </c>
-      <c r="F8" s="8" t="s">
+      <c r="F8" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G8" s="8"/>
+      <c r="G8" s="13"/>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B9" s="2">
@@ -3317,11 +3322,11 @@
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="B15" s="8" t="s">
+      <c r="B15" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="13"/>
       <c r="F15" s="3">
         <v>60</v>
       </c>
@@ -3423,10 +3428,10 @@
         <f t="shared" si="1"/>
         <v>10.090909090909092</v>
       </c>
-      <c r="F21" s="8" t="s">
+      <c r="F21" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="G21" s="8"/>
+      <c r="G21" s="13"/>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="F22" s="1" t="s">
@@ -3535,197 +3540,197 @@
   <dimension ref="B2:F14"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" style="10"/>
-    <col min="2" max="2" width="25.58203125" style="10" customWidth="1"/>
-    <col min="3" max="3" width="17.1640625" style="10" customWidth="1"/>
-    <col min="4" max="5" width="8.6640625" style="10"/>
-    <col min="6" max="6" width="38.58203125" style="10" customWidth="1"/>
-    <col min="7" max="16384" width="8.6640625" style="10"/>
+    <col min="1" max="1" width="8.6640625" style="9"/>
+    <col min="2" max="2" width="25.58203125" style="9" customWidth="1"/>
+    <col min="3" max="3" width="17.1640625" style="9" customWidth="1"/>
+    <col min="4" max="5" width="8.6640625" style="9"/>
+    <col min="6" max="6" width="38.58203125" style="9" customWidth="1"/>
+    <col min="7" max="16384" width="8.6640625" style="9"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" s="10" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B2" s="9" t="s">
+    <row r="2" spans="2:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="B2" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-    </row>
-    <row r="3" spans="2:6" s="10" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B3" s="11" t="s">
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+    </row>
+    <row r="3" spans="2:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="B3" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="E3" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="F3" s="10" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="2:6" s="10" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B4" s="10" t="s">
+    <row r="4" spans="2:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="B4" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="D4" s="10">
+      <c r="D4" s="9">
         <v>3</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="E4" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="F4" s="11" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="5" spans="2:6" s="10" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B5" s="10" t="s">
+    <row r="5" spans="2:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="B5" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="D5" s="10">
+      <c r="D5" s="9">
         <v>1</v>
       </c>
-      <c r="E5" s="10" t="s">
+      <c r="E5" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="F5" s="10" t="s">
+      <c r="F5" s="9" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="2:6" s="10" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B6" s="10" t="s">
+    <row r="6" spans="2:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="B6" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="D6" s="10">
+      <c r="D6" s="9">
         <v>1</v>
       </c>
-      <c r="E6" s="10" t="s">
+      <c r="E6" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="F6" s="10" t="s">
+      <c r="F6" s="9" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="7" spans="2:6" s="10" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B7" s="10" t="s">
+    <row r="7" spans="2:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="B7" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="10">
+      <c r="D7" s="9">
         <v>1</v>
       </c>
-      <c r="E7" s="10" t="s">
+      <c r="E7" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="F7" s="10" t="s">
+      <c r="F7" s="9" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="8" spans="2:6" s="10" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B8" s="10" t="s">
+    <row r="8" spans="2:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="B8" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="D8" s="10">
+      <c r="D8" s="9">
         <v>2</v>
       </c>
-      <c r="E8" s="10" t="s">
+      <c r="E8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="F8" s="10" t="s">
+      <c r="F8" s="9" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="9" spans="2:6" s="10" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B9" s="10" t="s">
+    <row r="9" spans="2:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="B9" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="D9" s="10">
+      <c r="D9" s="9">
         <v>1</v>
       </c>
-      <c r="E9" s="10" t="s">
+      <c r="E9" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="F9" s="10" t="s">
+      <c r="F9" s="9" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="10" spans="2:6" s="10" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B10" s="10" t="s">
+    <row r="10" spans="2:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="B10" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="D10" s="10">
+      <c r="D10" s="9">
         <v>2</v>
       </c>
-      <c r="E10" s="10" t="s">
+      <c r="E10" s="9" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="11" spans="2:6" s="10" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B11" s="10" t="s">
+    <row r="11" spans="2:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="B11" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="D11" s="10">
+      <c r="D11" s="9">
         <v>2</v>
       </c>
-      <c r="E11" s="10" t="s">
+      <c r="E11" s="9" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="12" spans="2:6" s="10" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B12" s="10" t="s">
+    <row r="12" spans="2:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="B12" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C12" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="D12" s="10">
+      <c r="D12" s="9">
         <v>1</v>
       </c>
-      <c r="E12" s="10" t="s">
+      <c r="E12" s="9" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="13" spans="2:6" s="10" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B13" s="10" t="s">
+    <row r="13" spans="2:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="B13" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="C13" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="D13" s="10">
+      <c r="D13" s="9">
         <v>1</v>
       </c>
-      <c r="E13" s="10" t="s">
+      <c r="E13" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="F13" s="10" t="s">
+      <c r="F13" s="9" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="14" spans="2:6" s="10" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B14" s="13" t="s">
+    <row r="14" spans="2:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="B14" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="C14" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="D14" s="13">
+      <c r="D14" s="8">
         <v>1</v>
       </c>
-      <c r="E14" s="13" t="s">
+      <c r="E14" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="F14" s="13" t="s">
+      <c r="F14" s="8" t="s">
         <v>48</v>
       </c>
     </row>

--- a/docs/データシート.xlsx
+++ b/docs/データシート.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yamashita\Documents\sensors-and-control\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7272ADF7-F6F9-4E46-9221-195CFD875705}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CCECC2A-AE60-4FAB-BEF9-D403E87112A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="11460" windowHeight="14410" xr2:uid="{D7E328D4-FD25-4938-8122-60FB433CDBB7}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{D7E328D4-FD25-4938-8122-60FB433CDBB7}"/>
   </bookViews>
   <sheets>
     <sheet name="1st" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="52">
   <si>
     <t>公称値</t>
     <rPh sb="0" eb="3">
@@ -67,30 +67,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>日中の窓際</t>
-    <rPh sb="0" eb="2">
-      <t>ニッチュウ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>マドギワ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>夜間室内</t>
-    <rPh sb="0" eb="4">
-      <t>ヤカンシツナイ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>暗黒</t>
-    <rPh sb="0" eb="2">
-      <t>アンコク</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>距離</t>
     <rPh sb="0" eb="2">
       <t>キョリ</t>
@@ -424,6 +400,66 @@
   </si>
   <si>
     <t>-</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>測定値[Ω]</t>
+    <rPh sb="0" eb="3">
+      <t>ソクテイチ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>日中の窓際（晴天・直射日光下）</t>
+    <rPh sb="0" eb="2">
+      <t>ニッチュウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>マドギワ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>セイテン</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>チョクシャ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ニッコウ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>シタ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>7.1k</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>暗闇</t>
+    <rPh sb="0" eb="2">
+      <t>クラヤミ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1.6M</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>夜間室内（照明点灯下）</t>
+    <rPh sb="0" eb="4">
+      <t>ヤカンシツナイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ショウメイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>テントウ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>シタ</t>
+    </rPh>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -555,10 +591,10 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -3108,21 +3144,21 @@
     <col min="3" max="3" width="13" style="2" customWidth="1"/>
     <col min="4" max="4" width="14.6640625" style="2" customWidth="1"/>
     <col min="5" max="5" width="8.6640625" style="2"/>
-    <col min="6" max="6" width="13.6640625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="30.6640625" style="2" customWidth="1"/>
     <col min="7" max="7" width="13.75" style="2" customWidth="1"/>
     <col min="8" max="16384" width="8.6640625" style="2"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="B2" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="F2" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="G2" s="13"/>
+      <c r="B2" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="F2" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" s="12"/>
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B3" s="1" t="s">
@@ -3138,7 +3174,7 @@
         <v>3</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>1</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.55000000000000004">
@@ -3153,7 +3189,7 @@
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>4</v>
+        <v>47</v>
       </c>
       <c r="G4" s="2">
         <v>114</v>
@@ -3171,10 +3207,10 @@
         <v>-2.9999999999999714E-3</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G5" s="2">
-        <v>70551</v>
+        <v>51</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.55000000000000004">
@@ -3189,10 +3225,10 @@
         <v>0</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G6" s="4">
-        <v>320000</v>
+        <v>49</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.55000000000000004">
@@ -3218,10 +3254,10 @@
         <f t="shared" si="0"/>
         <v>-2.8000000000000001E-2</v>
       </c>
-      <c r="F8" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G8" s="13"/>
+      <c r="F8" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="G8" s="12"/>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B9" s="2">
@@ -3235,10 +3271,10 @@
         <v>-0.02</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.55000000000000004">
@@ -3322,11 +3358,11 @@
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="B15" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13"/>
+      <c r="B15" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
       <c r="F15" s="3">
         <v>60</v>
       </c>
@@ -3336,13 +3372,13 @@
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B16" s="4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F16" s="3">
         <v>70</v>
@@ -3353,7 +3389,7 @@
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B17" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C17" s="2">
         <v>1.98</v>
@@ -3371,7 +3407,7 @@
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B18" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C18" s="2">
         <v>2.0499999999999998</v>
@@ -3389,7 +3425,7 @@
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B19" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C19" s="2">
         <v>2.74</v>
@@ -3407,7 +3443,7 @@
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B20" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C20" s="2">
         <v>2.74</v>
@@ -3419,7 +3455,7 @@
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B21" s="4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C21" s="4">
         <v>2.78</v>
@@ -3428,14 +3464,14 @@
         <f t="shared" si="1"/>
         <v>10.090909090909092</v>
       </c>
-      <c r="F21" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="G21" s="13"/>
+      <c r="F21" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G21" s="12"/>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="F22" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G22" s="1" t="s">
         <v>1</v>
@@ -3549,189 +3585,189 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B2" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
+      <c r="B2" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.55000000000000004">
       <c r="B3" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="F3" s="10" t="s">
         <v>25</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="E3" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="F3" s="10" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.55000000000000004">
       <c r="B4" s="9" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D4" s="9">
         <v>3</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.55000000000000004">
       <c r="B5" s="9" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D5" s="9">
         <v>1</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.55000000000000004">
       <c r="B6" s="9" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D6" s="9">
         <v>1</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.55000000000000004">
       <c r="B7" s="9" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D7" s="9">
         <v>1</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.55000000000000004">
       <c r="B8" s="9" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D8" s="9">
         <v>2</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.55000000000000004">
       <c r="B9" s="9" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D9" s="9">
         <v>1</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.55000000000000004">
       <c r="B10" s="9" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D10" s="9">
         <v>2</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.55000000000000004">
       <c r="B11" s="9" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D11" s="9">
         <v>2</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.55000000000000004">
       <c r="B12" s="9" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D12" s="9">
         <v>1</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.55000000000000004">
       <c r="B13" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" s="9" t="s">
         <v>38</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>41</v>
       </c>
       <c r="D13" s="9">
         <v>1</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.55000000000000004">
       <c r="B14" s="8" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D14" s="8">
         <v>1</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
